--- a/analisis-loteo-talca/Modelo_Loteo_Talca.xlsx
+++ b/analisis-loteo-talca/Modelo_Loteo_Talca.xlsx
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -818,27 +818,27 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35% para caber en el plazo de 5 años</t>
+          <t>30% de cada escritura</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Plazo máximo para pagar el terreno</t>
+          <t>Año de vencimiento del plazo</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>años</t>
+          <t>año</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Debe contarse desde el permiso de loteo</t>
+          <t>5 años desde el permiso, obtenido en el año 1</t>
         </is>
       </c>
     </row>
@@ -1005,17 +1005,17 @@
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>185000</v>
+        <v>80000</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>155000</v>
+        <v>60000</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>135000</v>
+        <v>45000</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>UF — cotizar con 3 contratistas</t>
+          <t>UF — reconstruido del resumen por km; cotizar en firme</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5390,467 +5390,551 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1150</v>
+        <v>619.2</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1400</v>
+        <v>619.2</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1600</v>
+        <v>619.2</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>~32% de ocupación del paño</t>
+          <t>L_05: 8 locales de 38,4 + 2 restaurantes de 156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Renta (UF/m²/mes)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0.42</v>
+          <t>Superficie construida total (m²)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>729.7</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>729.7</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>729.7</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Referencia RM: 0,69 en primer piso</t>
+          <t>Incluye administración y baños/camarines</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Vacancia</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Renta (UF/m²/mes)</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Referencia RM: 0,69 en primer piso</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Costo de construcción (UF/m²)</t>
+          <t>NOI de 4 canchas de pádel (UF/año)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>22</v>
+        <v>1350</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Shell &amp; core</t>
+          <t>Arrendadas a operador, sin operar</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Obras exteriores y empalmes (UF)</t>
+          <t>Inversión en canchas de pádel (UF)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Estacionamientos, paisajismo</t>
+          <t>4 canchas, cierres e iluminación</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Costos blandos</t>
+          <t>Vacancia</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Proyectos, permisos, gerencia</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Terreno asignado (UF)</t>
+          <t>Costo de construcción (UF/m²)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>2710</v>
+        <v>27</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2710</v>
+        <v>24</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>2710</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3% de las 119.000 UF</t>
+          <t>Shell &amp; core</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Gastos no recuperables</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0.12</v>
+          <t>Obras exteriores y empalmes (UF)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>4500</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Contribuciones, administración</t>
+          <t>Estacionamientos, paisajismo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Costos blandos</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Proyectos, permisos, gerencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Terreno asignado (UF)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>2710</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>2710</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,3% de las 119.000 UF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Gastos no recuperables</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Contribuciones, administración</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>Cap rate de salida</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B16" s="14" t="n">
         <v>0.095</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C16" s="14" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D16" s="14" t="n">
         <v>0.075</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Chile 5,8–7,5%; premio regional</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Inversión total (UF)</t>
-        </is>
-      </c>
-      <c r="B14" s="21">
-        <f>B5*B8*(1+B10)+B9+B11</f>
-        <v/>
-      </c>
-      <c r="C14" s="21">
-        <f>C5*C8*(1+C10)+C9+C11</f>
-        <v/>
-      </c>
-      <c r="D14" s="21">
-        <f>D5*D8*(1+D10)+D9+D11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Renta bruta anual (UF)</t>
-        </is>
-      </c>
-      <c r="B15" s="21">
-        <f>B5*B6*12</f>
-        <v/>
-      </c>
-      <c r="C15" s="21">
-        <f>C5*C6*12</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>D5*D6*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NOI anual (UF)</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>B15*(1-B7)*(1-B12)</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
-        <f>C15*(1-C7)*(1-C12)</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>D15*(1-D7)*(1-D12)</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Yield on cost</t>
-        </is>
-      </c>
-      <c r="B17" s="22">
-        <f>B16/B14</f>
-        <v/>
-      </c>
-      <c r="C17" s="22">
-        <f>C16/C14</f>
-        <v/>
-      </c>
-      <c r="D17" s="22">
-        <f>D16/D14</f>
+          <t>Inversión total (UF)</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>B6*B11*(1+B13)+B9+B12+B14</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>C6*C11*(1+C13)+C9+C12+C14</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>D6*D11*(1+D13)+D9+D12+D14</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Valor estabilizado (UF)</t>
+          <t>Renta bruta anual (UF)</t>
         </is>
       </c>
       <c r="B18" s="21">
-        <f>B16/B13</f>
+        <f>B5*B7*12</f>
         <v/>
       </c>
       <c r="C18" s="21">
-        <f>C16/C13</f>
+        <f>C5*C7*12</f>
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>D16/D13</f>
+        <f>D5*D7*12</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Creación de valor (UF)</t>
+          <t>NOI anual (UF)</t>
         </is>
       </c>
       <c r="B19" s="21">
-        <f>B18-B14</f>
+        <f>B18*(1-B10)*(1-B15)+B8</f>
         <v/>
       </c>
       <c r="C19" s="21">
-        <f>C18-C14</f>
+        <f>C18*(1-C10)*(1-C15)+C8</f>
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>D18-D14</f>
+        <f>D18*(1-D10)*(1-D15)+D8</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
+          <t>Yield on cost</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>B19/B17</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f>C19/C17</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>D19/D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Valor estabilizado (UF)</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>B19/B16</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>C19/C16</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>D19/D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Creación de valor (UF)</t>
+        </is>
+      </c>
+      <c r="B22" s="21">
+        <f>B21-B17</f>
+        <v/>
+      </c>
+      <c r="C22" s="21">
+        <f>C21-C17</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>D21-D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>Payback (años)</t>
         </is>
       </c>
-      <c r="B20" s="24">
-        <f>B14/B16</f>
-        <v/>
-      </c>
-      <c r="C20" s="24">
-        <f>C14/C16</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>D14/D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B23" s="24">
+        <f>B17/B19</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>C17/C19</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>D17/D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>ETAPA 3 — COMPARACIÓN DE ALTERNATIVAS PARA EL PAÑO NORTE (18.619 m²)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Colegio build-to-suit</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Venta del paño</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>EDS arrendada</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Inversión propia (UF)</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n">
-        <v>255102</v>
-      </c>
-      <c r="C25" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>4859</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>EDS: sólo accesos, EISTU y empalmes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Flujo anual (UF)</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n">
-        <v>22230</v>
-      </c>
-      <c r="C26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>4200</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>EDS: canon de 350 UF/mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Rentabilidad sobre costo</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="C27" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="26" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Valor del activo (UF)</t>
+          <t>Inversión propia (UF)</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
-        <v>261529</v>
+        <v>177894</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>46548</v>
+        <v>0</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>56000</v>
+        <v>4879</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Venta del paño a 2,5 UF/m²</t>
+          <t>Colegio L_09: 3.849 m² cerrados + 2.088 patio techado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Payback (años)</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="C29" s="27" t="n">
+          <t>Flujo anual (UF)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>12286</v>
+      </c>
+      <c r="C29" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="D29" s="25" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>EDS: canon de 350 UF/mes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Rentabilidad sobre costo</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Valor del activo (UF)</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>144541</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>45885</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <v>56000</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Venta del paño a 2,5 UF/m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Creación de valor (UF)</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>-33352</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>34383</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <v>51121</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>El colegio destruye valor en escenario Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Payback (años)</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Superficie que ocupa (m²)</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
-        <v>18619</v>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>18619</v>
-      </c>
-      <c r="D30" s="25" t="n">
+      <c r="B34" s="25" t="n">
+        <v>18354</v>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>18354</v>
+      </c>
+      <c r="D34" s="25" t="n">
         <v>2200</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>La EDS deja 16.400 m² libres</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>La EDS deja 16.154 m² libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>Requisito duro para la EDS: TMDA de Av. San Miguel sobre 8.000–12.000 veh/día para atraer a un operador de marca. Verificar en Dirección de Vialidad del Maule.</t>
         </is>

--- a/analisis-loteo-talca/Modelo_Loteo_Talca.xlsx
+++ b/analisis-loteo-talca/Modelo_Loteo_Talca.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Supuestos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Flujo Conservador" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Flujo Base" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Flujo Optimista" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Etapas 2 y 3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Conservador" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Base" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Optimista" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Etapas 2 y 3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C3B2E"/>
       <sz val="9"/>
     </font>
     <font>
@@ -104,46 +109,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -153,7 +159,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,47 +550,54 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Verificado contra la tabla de escenarios del informe: capital máximo idéntico, ingresos y utilidad dentro de ±5%, TIR entre 2 y 4 puntos más baja. La diferencia viene de dos simplificaciones: el precio maduro se mantiene constante (el informe lo sube 0,1 UF/m² al año desde el cuarto año de venta) y el impuesto se devenga anual, no por venta.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>DATOS DUROS (planos L_02 / L_03, agosto 2023)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Paño fusionado</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>192627</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -596,15 +609,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Superficie de los 90 sitios</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>127866</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -616,15 +629,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>N° de sitios</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>u</t>
         </is>
@@ -636,15 +649,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Paño colegio</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>18619</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -656,15 +669,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Paño locales comerciales</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>4386</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -676,15 +689,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Áreas verdes</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>13798</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -696,15 +709,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Vialidad + expropiación</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>27958</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -721,8 +734,8 @@
           <t>Superficie promedio por sitio</t>
         </is>
       </c>
-      <c r="B13" s="8">
-        <f>B6/B7</f>
+      <c r="B13" s="9">
+        <f>B7/B8</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr">
@@ -732,46 +745,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>INPUTS — TERRENO</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Precio del terreno</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="10" t="n">
         <v>119000</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>UF</t>
         </is>
@@ -783,35 +796,35 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Pie</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B18" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>UF</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Propuesto: 10.000 en vez de 20.000</t>
+          <t>Bajarlo a 10.000 es la recomendación: sube la TIR ~3 puntos</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>% de cada venta destinado al terreno</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -823,15 +836,15 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Año de vencimiento del plazo</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>año</t>
         </is>
@@ -848,7 +861,7 @@
           <t>Saldo contra flujo</t>
         </is>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="9">
         <f>B17-B18</f>
         <v/>
       </c>
@@ -859,53 +872,53 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>INPUTS — ESCENARIOS</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Sitios vendidos por año</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="12" t="n">
         <v>21</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -915,18 +928,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Año de inicio de ventas</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -936,18 +949,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Precio inicial</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <v>3.3</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="14" t="n">
         <v>3.5</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>3.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -957,18 +970,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Precio maduro</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="14" t="n">
         <v>3.8</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>4.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -978,18 +991,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Año de venta en que sube el precio</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="13" t="n">
         <v>2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -999,18 +1012,18 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Urbanización total (IVA incluido)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="12" t="n">
         <v>60000</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="12" t="n">
         <v>45000</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1020,18 +1033,18 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Gasto comercial</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>0.055</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="15" t="n">
         <v>0.045</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="15" t="n">
         <v>0.04</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1041,18 +1054,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Administración anual</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
+      <c r="B32" s="12" t="n">
         <v>3000</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="12" t="n">
         <v>2500</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1062,18 +1075,18 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Proyectos y permisos año 0</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B33" s="12" t="n">
         <v>9000</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="12" t="n">
         <v>9000</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="12" t="n">
         <v>9000</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1083,18 +1096,18 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Proyectos y permisos año 1</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1104,18 +1117,18 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Contribuciones anuales</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B35" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="12" t="n">
         <v>500</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1125,18 +1138,18 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Impuesto a la renta</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B36" s="16" t="n">
         <v>0.27</v>
       </c>
-      <c r="C36" s="15" t="n">
+      <c r="C36" s="16" t="n">
         <v>0.27</v>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>0.27</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1146,18 +1159,18 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Tasa de descuento</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
+      <c r="B37" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="C37" s="15" t="n">
+      <c r="C37" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1167,23 +1180,23 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Preventa cobrada un año antes</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>0.2</v>
+      <c r="B38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Pie de promesa</t>
+          <t>Subir a 20% para ver la estructura optimizada</t>
         </is>
       </c>
     </row>
@@ -1235,144 +1248,144 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Año 11</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Año 12</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>Año 13</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Año 14</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>Año 15</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="16" t="n">
+      <c r="M5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1382,139 +1395,139 @@
           <t>Sitios vendidos acumulados (previo)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <f>0</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <f>F6+F7</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <f>G6+G7</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
         <f>H6+H7</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="9">
         <f>I6+I7</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="9">
         <f>J6+J7</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="9">
         <f>K6+K7</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="9">
         <f>L6+L7</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="9">
         <f>M6+M7</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>N6+N7</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="9">
         <f>O6+O7</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="9">
         <f>P6+P7</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Sitios vendidos en el año</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>IF(0&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-B6))</f>
-        <v/>
-      </c>
-      <c r="C7" s="8">
-        <f>IF(1&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-C6))</f>
-        <v/>
-      </c>
-      <c r="D7" s="8">
-        <f>IF(2&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-D6))</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>IF(3&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-E6))</f>
-        <v/>
-      </c>
-      <c r="F7" s="8">
-        <f>IF(4&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-F6))</f>
-        <v/>
-      </c>
-      <c r="G7" s="8">
-        <f>IF(5&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-G6))</f>
-        <v/>
-      </c>
-      <c r="H7" s="8">
-        <f>IF(6&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-H6))</f>
-        <v/>
-      </c>
-      <c r="I7" s="8">
-        <f>IF(7&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-I6))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8">
-        <f>IF(8&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-J6))</f>
-        <v/>
-      </c>
-      <c r="K7" s="8">
-        <f>IF(9&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-K6))</f>
-        <v/>
-      </c>
-      <c r="L7" s="8">
-        <f>IF(10&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-L6))</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
-        <f>IF(11&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-M6))</f>
-        <v/>
-      </c>
-      <c r="N7" s="8">
-        <f>IF(12&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-N6))</f>
-        <v/>
-      </c>
-      <c r="O7" s="8">
-        <f>IF(13&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-O6))</f>
-        <v/>
-      </c>
-      <c r="P7" s="8">
-        <f>IF(14&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-P6))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8">
-        <f>IF(15&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$7-Q6))</f>
+      <c r="B7" s="9">
+        <f>IF(0&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>IF(1&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>IF(2&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>IF(3&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>IF(4&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-F6))</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(5&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-G6))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(6&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-H6))</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>IF(7&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-I6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>IF(8&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-J6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>IF(9&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-K6))</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IF(10&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-L6))</f>
+        <v/>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(11&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-M6))</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(12&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-N6))</f>
+        <v/>
+      </c>
+      <c r="O7" s="9">
+        <f>IF(13&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-O6))</f>
+        <v/>
+      </c>
+      <c r="P7" s="9">
+        <f>IF(14&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-P6))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="9">
+        <f>IF(15&lt;Supuestos!$B$26,0,MIN(Supuestos!$B$25,Supuestos!$B$8-Q6))</f>
         <v/>
       </c>
     </row>
@@ -1524,138 +1537,138 @@
           <t>Precio del año (UF/m²)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>IF(0&lt;Supuestos!$B$26,0,IF(0-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>IF(1&lt;Supuestos!$B$26,0,IF(1-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF(2&lt;Supuestos!$B$26,0,IF(2-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>IF(3&lt;Supuestos!$B$26,0,IF(3-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF(4&lt;Supuestos!$B$26,0,IF(4-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>IF(5&lt;Supuestos!$B$26,0,IF(5-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="18">
         <f>IF(6&lt;Supuestos!$B$26,0,IF(6-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="18">
         <f>IF(7&lt;Supuestos!$B$26,0,IF(7-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="18">
         <f>IF(8&lt;Supuestos!$B$26,0,IF(8-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="18">
         <f>IF(9&lt;Supuestos!$B$26,0,IF(9-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="18">
         <f>IF(10&lt;Supuestos!$B$26,0,IF(10-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="18">
         <f>IF(11&lt;Supuestos!$B$26,0,IF(11-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <f>IF(12&lt;Supuestos!$B$26,0,IF(12-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="18">
         <f>IF(13&lt;Supuestos!$B$26,0,IF(13-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="18">
         <f>IF(14&lt;Supuestos!$B$26,0,IF(14-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="18">
         <f>IF(15&lt;Supuestos!$B$26,0,IF(15-Supuestos!$B$26+1&gt;=Supuestos!$B$29,Supuestos!$B$28,Supuestos!$B$27))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Ingresos por venta</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <f>B7*Supuestos!$B$13*B8</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <f>C7*Supuestos!$B$13*C8</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>D7*Supuestos!$B$13*D8</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <f>E7*Supuestos!$B$13*E8</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <f>F7*Supuestos!$B$13*F8</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <f>G7*Supuestos!$B$13*G8</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <f>H7*Supuestos!$B$13*H8</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="9">
         <f>I7*Supuestos!$B$13*I8</f>
         <v/>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9">
         <f>J7*Supuestos!$B$13*J8</f>
         <v/>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="9">
         <f>K7*Supuestos!$B$13*K8</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="9">
         <f>L7*Supuestos!$B$13*L8</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="9">
         <f>M7*Supuestos!$B$13*M8</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="9">
         <f>N7*Supuestos!$B$13*N8</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>O7*Supuestos!$B$13*O8</f>
         <v/>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="9">
         <f>P7*Supuestos!$B$13*P8</f>
         <v/>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="9">
         <f>Q7*Supuestos!$B$13*Q8</f>
         <v/>
       </c>
@@ -1666,67 +1679,67 @@
           <t>Caja por ventas (20% anticipado)</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <f>B9*(1-Supuestos!$B$38)+C9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <f>C9*(1-Supuestos!$B$38)+D9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>D9*(1-Supuestos!$B$38)+E9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <f>E9*(1-Supuestos!$B$38)+F9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <f>F9*(1-Supuestos!$B$38)+G9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <f>G9*(1-Supuestos!$B$38)+H9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>H9*(1-Supuestos!$B$38)+I9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <f>I9*(1-Supuestos!$B$38)+J9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <f>J9*(1-Supuestos!$B$38)+K9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <f>K9*(1-Supuestos!$B$38)+L9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="9">
         <f>L9*(1-Supuestos!$B$38)+M9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="9">
         <f>M9*(1-Supuestos!$B$38)+N9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="9">
         <f>N9*(1-Supuestos!$B$38)+O9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>O9*(1-Supuestos!$B$38)+P9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="9">
         <f>P9*(1-Supuestos!$B$38)+Q9*Supuestos!$B$38</f>
         <v/>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="9">
         <f>Q9*(1-Supuestos!$B$38)</f>
         <v/>
       </c>
@@ -1734,71 +1747,71 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Urbanización (4 macro-etapas)</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Supuestos!$B$30*(IF(0=Supuestos!$B$26-1,0.3,0)+IF(0=Supuestos!$B$26,0.25,0)+IF(0=Supuestos!$B$26+2,0.25,0)+IF(0=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="C12" s="8">
-        <f>Supuestos!$B$30*(IF(1=Supuestos!$B$26-1,0.3,0)+IF(1=Supuestos!$B$26,0.25,0)+IF(1=Supuestos!$B$26+2,0.25,0)+IF(1=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="D12" s="8">
-        <f>Supuestos!$B$30*(IF(2=Supuestos!$B$26-1,0.3,0)+IF(2=Supuestos!$B$26,0.25,0)+IF(2=Supuestos!$B$26+2,0.25,0)+IF(2=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>Supuestos!$B$30*(IF(3=Supuestos!$B$26-1,0.3,0)+IF(3=Supuestos!$B$26,0.25,0)+IF(3=Supuestos!$B$26+2,0.25,0)+IF(3=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="F12" s="8">
-        <f>Supuestos!$B$30*(IF(4=Supuestos!$B$26-1,0.3,0)+IF(4=Supuestos!$B$26,0.25,0)+IF(4=Supuestos!$B$26+2,0.25,0)+IF(4=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>Supuestos!$B$30*(IF(5=Supuestos!$B$26-1,0.3,0)+IF(5=Supuestos!$B$26,0.25,0)+IF(5=Supuestos!$B$26+2,0.25,0)+IF(5=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>Supuestos!$B$30*(IF(6=Supuestos!$B$26-1,0.3,0)+IF(6=Supuestos!$B$26,0.25,0)+IF(6=Supuestos!$B$26+2,0.25,0)+IF(6=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="I12" s="8">
-        <f>Supuestos!$B$30*(IF(7=Supuestos!$B$26-1,0.3,0)+IF(7=Supuestos!$B$26,0.25,0)+IF(7=Supuestos!$B$26+2,0.25,0)+IF(7=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>Supuestos!$B$30*(IF(8=Supuestos!$B$26-1,0.3,0)+IF(8=Supuestos!$B$26,0.25,0)+IF(8=Supuestos!$B$26+2,0.25,0)+IF(8=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
-        <f>Supuestos!$B$30*(IF(9=Supuestos!$B$26-1,0.3,0)+IF(9=Supuestos!$B$26,0.25,0)+IF(9=Supuestos!$B$26+2,0.25,0)+IF(9=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="L12" s="8">
-        <f>Supuestos!$B$30*(IF(10=Supuestos!$B$26-1,0.3,0)+IF(10=Supuestos!$B$26,0.25,0)+IF(10=Supuestos!$B$26+2,0.25,0)+IF(10=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="M12" s="8">
-        <f>Supuestos!$B$30*(IF(11=Supuestos!$B$26-1,0.3,0)+IF(11=Supuestos!$B$26,0.25,0)+IF(11=Supuestos!$B$26+2,0.25,0)+IF(11=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="N12" s="8">
-        <f>Supuestos!$B$30*(IF(12=Supuestos!$B$26-1,0.3,0)+IF(12=Supuestos!$B$26,0.25,0)+IF(12=Supuestos!$B$26+2,0.25,0)+IF(12=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="O12" s="8">
-        <f>Supuestos!$B$30*(IF(13=Supuestos!$B$26-1,0.3,0)+IF(13=Supuestos!$B$26,0.25,0)+IF(13=Supuestos!$B$26+2,0.25,0)+IF(13=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="P12" s="8">
-        <f>Supuestos!$B$30*(IF(14=Supuestos!$B$26-1,0.3,0)+IF(14=Supuestos!$B$26,0.25,0)+IF(14=Supuestos!$B$26+2,0.25,0)+IF(14=Supuestos!$B$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8">
-        <f>Supuestos!$B$30*(IF(15=Supuestos!$B$26-1,0.3,0)+IF(15=Supuestos!$B$26,0.25,0)+IF(15=Supuestos!$B$26+2,0.25,0)+IF(15=Supuestos!$B$26+4,0.2,0))</f>
+          <t>Urbanización (3 macro-etapas)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Supuestos!$B$30*(IF(0=Supuestos!$B$26-1,0.45,0)+IF(0=Supuestos!$B$26+1,0.3,0)+IF(0=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>Supuestos!$B$30*(IF(1=Supuestos!$B$26-1,0.45,0)+IF(1=Supuestos!$B$26+1,0.3,0)+IF(1=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>Supuestos!$B$30*(IF(2=Supuestos!$B$26-1,0.45,0)+IF(2=Supuestos!$B$26+1,0.3,0)+IF(2=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>Supuestos!$B$30*(IF(3=Supuestos!$B$26-1,0.45,0)+IF(3=Supuestos!$B$26+1,0.3,0)+IF(3=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>Supuestos!$B$30*(IF(4=Supuestos!$B$26-1,0.45,0)+IF(4=Supuestos!$B$26+1,0.3,0)+IF(4=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>Supuestos!$B$30*(IF(5=Supuestos!$B$26-1,0.45,0)+IF(5=Supuestos!$B$26+1,0.3,0)+IF(5=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>Supuestos!$B$30*(IF(6=Supuestos!$B$26-1,0.45,0)+IF(6=Supuestos!$B$26+1,0.3,0)+IF(6=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>Supuestos!$B$30*(IF(7=Supuestos!$B$26-1,0.45,0)+IF(7=Supuestos!$B$26+1,0.3,0)+IF(7=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>Supuestos!$B$30*(IF(8=Supuestos!$B$26-1,0.45,0)+IF(8=Supuestos!$B$26+1,0.3,0)+IF(8=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>Supuestos!$B$30*(IF(9=Supuestos!$B$26-1,0.45,0)+IF(9=Supuestos!$B$26+1,0.3,0)+IF(9=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>Supuestos!$B$30*(IF(10=Supuestos!$B$26-1,0.45,0)+IF(10=Supuestos!$B$26+1,0.3,0)+IF(10=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="9">
+        <f>Supuestos!$B$30*(IF(11=Supuestos!$B$26-1,0.45,0)+IF(11=Supuestos!$B$26+1,0.3,0)+IF(11=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>Supuestos!$B$30*(IF(12=Supuestos!$B$26-1,0.45,0)+IF(12=Supuestos!$B$26+1,0.3,0)+IF(12=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="O12" s="9">
+        <f>Supuestos!$B$30*(IF(13=Supuestos!$B$26-1,0.45,0)+IF(13=Supuestos!$B$26+1,0.3,0)+IF(13=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="P12" s="9">
+        <f>Supuestos!$B$30*(IF(14=Supuestos!$B$26-1,0.45,0)+IF(14=Supuestos!$B$26+1,0.3,0)+IF(14=Supuestos!$B$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9">
+        <f>Supuestos!$B$30*(IF(15=Supuestos!$B$26-1,0.45,0)+IF(15=Supuestos!$B$26+1,0.3,0)+IF(15=Supuestos!$B$26+3,0.25,0))</f>
         <v/>
       </c>
     </row>
@@ -1808,54 +1821,54 @@
           <t>Proyectos, permisos y especialidades</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>Supuestos!$B$33</f>
         <v/>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <f>Supuestos!$B$34</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="P13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1865,67 +1878,67 @@
           <t>Gasto comercial</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <f>B9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>O9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="9">
         <f>P9*Supuestos!$B$31</f>
         <v/>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="9">
         <f>Q9*Supuestos!$B$31</f>
         <v/>
       </c>
@@ -1936,209 +1949,209 @@
           <t>Administración y contribuciones</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <f>IF(OR(B7&gt;0,0&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>IF(OR(C7&gt;0,1&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>IF(OR(D7&gt;0,2&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>IF(OR(E7&gt;0,3&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>IF(OR(F7&gt;0,4&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>IF(OR(G7&gt;0,5&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>IF(OR(H7&gt;0,6&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>IF(OR(I7&gt;0,7&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>IF(OR(J7&gt;0,8&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>IF(OR(K7&gt;0,9&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>IF(OR(L7&gt;0,10&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>IF(OR(M7&gt;0,11&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>IF(OR(N7&gt;0,12&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="9">
         <f>IF(OR(O7&gt;0,13&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="9">
         <f>IF(OR(P7&gt;0,14&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="9">
         <f>IF(OR(Q7&gt;0,15&lt;Supuestos!$B$26),Supuestos!$B$32+Supuestos!$B$35,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Total egresos operacionales</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B12+B13+B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>C12+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>D12+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>E12+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>F12+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>G12+G13+G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>H12+H13+H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>I12+I13+I14+I15</f>
         <v/>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>J12+J13+J14+J15</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f>K12+K13+K14+K15</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>L12+L13+L14+L15</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="20">
         <f>M12+M13+M14+M15</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="20">
         <f>N12+N13+N14+N15</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="20">
         <f>O12+O13+O14+O15</f>
         <v/>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="20">
         <f>P12+P13+P14+P15</f>
         <v/>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="20">
         <f>Q12+Q13+Q14+Q15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Pago del terreno</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <f>Supuestos!$B$18</f>
         <v/>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>IF(1&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:B18)),MIN(C10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:B18))))</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f>IF(2&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:C18)),MIN(D10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:C18))))</f>
         <v/>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <f>IF(3&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:D18)),MIN(E10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:D18))))</f>
         <v/>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <f>IF(4&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:E18)),MIN(F10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:E18))))</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <f>IF(5&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:F18)),MIN(G10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:F18))))</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <f>IF(6&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:G18)),MIN(H10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:G18))))</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <f>IF(7&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:H18)),MIN(I10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:H18))))</f>
         <v/>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="9">
         <f>IF(8&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:I18)),MIN(J10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:I18))))</f>
         <v/>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <f>IF(9&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:J18)),MIN(K10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:J18))))</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="9">
         <f>IF(10&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:K18)),MIN(L10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:K18))))</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <f>IF(11&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:L18)),MIN(M10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:L18))))</f>
         <v/>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="9">
         <f>IF(12&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:M18)),MIN(N10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:M18))))</f>
         <v/>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="9">
         <f>IF(13&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:N18)),MIN(O10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:N18))))</f>
         <v/>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="9">
         <f>IF(14&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:O18)),MIN(P10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:O18))))</f>
         <v/>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="9">
         <f>IF(15&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:P18)),MIN(Q10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:P18))))</f>
         <v/>
       </c>
@@ -2149,67 +2162,67 @@
           <t>Saldo del terreno pendiente</t>
         </is>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:B18))</f>
         <v/>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:C18))</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:D18))</f>
         <v/>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:E18))</f>
         <v/>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:F18))</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:G18))</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:H18))</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:I18))</f>
         <v/>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:J18))</f>
         <v/>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:K18))</f>
         <v/>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:L18))</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:M18))</f>
         <v/>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:N18))</f>
         <v/>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:O18))</f>
         <v/>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:P18))</f>
         <v/>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:Q18))</f>
         <v/>
       </c>
@@ -2220,347 +2233,347 @@
           <t>Impuesto a la renta (pagado al año siguiente)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="8">
-        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8">
-        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="J20" s="8">
-        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="K20" s="8">
-        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="L20" s="8">
-        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="M20" s="8">
-        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="N20" s="8">
-        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="O20" s="8">
-        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="P20" s="8">
-        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="8">
-        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$B$36)</f>
+      <c r="C20" s="9">
+        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="K20" s="9">
+        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="L20" s="9">
+        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="M20" s="9">
+        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="N20" s="9">
+        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="O20" s="9">
+        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="P20" s="9">
+        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9">
+        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$B$36)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>FLUJO DE CAJA DEL PERÍODO</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="22">
         <f>B10-B16-B18-B20</f>
         <v/>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>C10-C16-C18-C20</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>D10-D16-D18-D20</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="22">
         <f>E10-E16-E18-E20</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="22">
         <f>F10-F16-F18-F20</f>
         <v/>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="22">
         <f>G10-G16-G18-G20</f>
         <v/>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <f>H10-H16-H18-H20</f>
         <v/>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <f>I10-I16-I18-I20</f>
         <v/>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="22">
         <f>J10-J16-J18-J20</f>
         <v/>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="22">
         <f>K10-K16-K18-K20</f>
         <v/>
       </c>
-      <c r="L22" s="21">
+      <c r="L22" s="22">
         <f>L10-L16-L18-L20</f>
         <v/>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="22">
         <f>M10-M16-M18-M20</f>
         <v/>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="22">
         <f>N10-N16-N18-N20</f>
         <v/>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="22">
         <f>O10-O16-O18-O20</f>
         <v/>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="22">
         <f>P10-P16-P18-P20</f>
         <v/>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="22">
         <f>Q10-Q16-Q18-Q20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Flujo acumulado</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <f>B22</f>
         <v/>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <f>B23+C22</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <f>C23+D22</f>
         <v/>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <f>D23+E22</f>
         <v/>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <f>E23+F22</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <f>F23+G22</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="9">
         <f>G23+H22</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f>H23+I22</f>
         <v/>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="9">
         <f>I23+J22</f>
         <v/>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <f>J23+K22</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>K23+L22</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f>L23+M22</f>
         <v/>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="9">
         <f>M23+N22</f>
         <v/>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="9">
         <f>N23+O22</f>
         <v/>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="9">
         <f>O23+P22</f>
         <v/>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="9">
         <f>P23+Q22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>INDICADORES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Ingresos totales</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="22">
         <f>SUM(B9:Q9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Costos totales (con terreno)</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="22">
         <f>SUM(B16:Q16)+Supuestos!$B$17*0.881</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Utilidad antes de impuesto</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="22">
         <f>B26-B27</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Margen bruto</t>
         </is>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="23">
         <f>B28/B26</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Impuesto</t>
         </is>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="22">
         <f>B28*Supuestos!$B$36</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Utilidad neta</t>
         </is>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="22">
         <f>B28-B30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Margen neto</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>B31/B26</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Capital máximo expuesto</t>
         </is>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="22">
         <f>-MIN(B23:Q23,0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>TIR del proyecto</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <f>IRR(B22:Q22)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>VAN a la tasa de descuento</t>
         </is>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <f>NPV(Supuestos!$B$37,C22:Q22)+B22</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Precio promedio logrado (UF/m²)</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>B26/Supuestos!$B$6</f>
+      <c r="B36" s="24">
+        <f>B26/Supuestos!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Saldo impago al vencer el plazo</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <f>INDEX(B19:Q19,Supuestos!$B$20+1)</f>
         <v/>
       </c>
@@ -2613,144 +2626,144 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Año 11</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Año 12</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>Año 13</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Año 14</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>Año 15</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="16" t="n">
+      <c r="M5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2760,139 +2773,139 @@
           <t>Sitios vendidos acumulados (previo)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <f>0</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <f>F6+F7</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <f>G6+G7</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
         <f>H6+H7</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="9">
         <f>I6+I7</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="9">
         <f>J6+J7</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="9">
         <f>K6+K7</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="9">
         <f>L6+L7</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="9">
         <f>M6+M7</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>N6+N7</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="9">
         <f>O6+O7</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="9">
         <f>P6+P7</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Sitios vendidos en el año</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>IF(0&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-B6))</f>
-        <v/>
-      </c>
-      <c r="C7" s="8">
-        <f>IF(1&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-C6))</f>
-        <v/>
-      </c>
-      <c r="D7" s="8">
-        <f>IF(2&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-D6))</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>IF(3&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-E6))</f>
-        <v/>
-      </c>
-      <c r="F7" s="8">
-        <f>IF(4&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-F6))</f>
-        <v/>
-      </c>
-      <c r="G7" s="8">
-        <f>IF(5&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-G6))</f>
-        <v/>
-      </c>
-      <c r="H7" s="8">
-        <f>IF(6&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-H6))</f>
-        <v/>
-      </c>
-      <c r="I7" s="8">
-        <f>IF(7&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-I6))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8">
-        <f>IF(8&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-J6))</f>
-        <v/>
-      </c>
-      <c r="K7" s="8">
-        <f>IF(9&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-K6))</f>
-        <v/>
-      </c>
-      <c r="L7" s="8">
-        <f>IF(10&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-L6))</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
-        <f>IF(11&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-M6))</f>
-        <v/>
-      </c>
-      <c r="N7" s="8">
-        <f>IF(12&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-N6))</f>
-        <v/>
-      </c>
-      <c r="O7" s="8">
-        <f>IF(13&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-O6))</f>
-        <v/>
-      </c>
-      <c r="P7" s="8">
-        <f>IF(14&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-P6))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8">
-        <f>IF(15&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$7-Q6))</f>
+      <c r="B7" s="9">
+        <f>IF(0&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>IF(1&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>IF(2&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>IF(3&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>IF(4&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-F6))</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(5&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-G6))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(6&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-H6))</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>IF(7&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-I6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>IF(8&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-J6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>IF(9&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-K6))</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IF(10&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-L6))</f>
+        <v/>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(11&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-M6))</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(12&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-N6))</f>
+        <v/>
+      </c>
+      <c r="O7" s="9">
+        <f>IF(13&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-O6))</f>
+        <v/>
+      </c>
+      <c r="P7" s="9">
+        <f>IF(14&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-P6))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="9">
+        <f>IF(15&lt;Supuestos!$C$26,0,MIN(Supuestos!$C$25,Supuestos!$B$8-Q6))</f>
         <v/>
       </c>
     </row>
@@ -2902,138 +2915,138 @@
           <t>Precio del año (UF/m²)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>IF(0&lt;Supuestos!$C$26,0,IF(0-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>IF(1&lt;Supuestos!$C$26,0,IF(1-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF(2&lt;Supuestos!$C$26,0,IF(2-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>IF(3&lt;Supuestos!$C$26,0,IF(3-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF(4&lt;Supuestos!$C$26,0,IF(4-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>IF(5&lt;Supuestos!$C$26,0,IF(5-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="18">
         <f>IF(6&lt;Supuestos!$C$26,0,IF(6-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="18">
         <f>IF(7&lt;Supuestos!$C$26,0,IF(7-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="18">
         <f>IF(8&lt;Supuestos!$C$26,0,IF(8-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="18">
         <f>IF(9&lt;Supuestos!$C$26,0,IF(9-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="18">
         <f>IF(10&lt;Supuestos!$C$26,0,IF(10-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="18">
         <f>IF(11&lt;Supuestos!$C$26,0,IF(11-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <f>IF(12&lt;Supuestos!$C$26,0,IF(12-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="18">
         <f>IF(13&lt;Supuestos!$C$26,0,IF(13-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="18">
         <f>IF(14&lt;Supuestos!$C$26,0,IF(14-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="18">
         <f>IF(15&lt;Supuestos!$C$26,0,IF(15-Supuestos!$C$26+1&gt;=Supuestos!$C$29,Supuestos!$C$28,Supuestos!$C$27))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Ingresos por venta</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <f>B7*Supuestos!$B$13*B8</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <f>C7*Supuestos!$B$13*C8</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>D7*Supuestos!$B$13*D8</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <f>E7*Supuestos!$B$13*E8</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <f>F7*Supuestos!$B$13*F8</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <f>G7*Supuestos!$B$13*G8</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <f>H7*Supuestos!$B$13*H8</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="9">
         <f>I7*Supuestos!$B$13*I8</f>
         <v/>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9">
         <f>J7*Supuestos!$B$13*J8</f>
         <v/>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="9">
         <f>K7*Supuestos!$B$13*K8</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="9">
         <f>L7*Supuestos!$B$13*L8</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="9">
         <f>M7*Supuestos!$B$13*M8</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="9">
         <f>N7*Supuestos!$B$13*N8</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>O7*Supuestos!$B$13*O8</f>
         <v/>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="9">
         <f>P7*Supuestos!$B$13*P8</f>
         <v/>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="9">
         <f>Q7*Supuestos!$B$13*Q8</f>
         <v/>
       </c>
@@ -3044,67 +3057,67 @@
           <t>Caja por ventas (20% anticipado)</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <f>B9*(1-Supuestos!$C$38)+C9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <f>C9*(1-Supuestos!$C$38)+D9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>D9*(1-Supuestos!$C$38)+E9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <f>E9*(1-Supuestos!$C$38)+F9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <f>F9*(1-Supuestos!$C$38)+G9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <f>G9*(1-Supuestos!$C$38)+H9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>H9*(1-Supuestos!$C$38)+I9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <f>I9*(1-Supuestos!$C$38)+J9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <f>J9*(1-Supuestos!$C$38)+K9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <f>K9*(1-Supuestos!$C$38)+L9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="9">
         <f>L9*(1-Supuestos!$C$38)+M9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="9">
         <f>M9*(1-Supuestos!$C$38)+N9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="9">
         <f>N9*(1-Supuestos!$C$38)+O9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>O9*(1-Supuestos!$C$38)+P9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="9">
         <f>P9*(1-Supuestos!$C$38)+Q9*Supuestos!$C$38</f>
         <v/>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="9">
         <f>Q9*(1-Supuestos!$C$38)</f>
         <v/>
       </c>
@@ -3112,71 +3125,71 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Urbanización (4 macro-etapas)</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Supuestos!$C$30*(IF(0=Supuestos!$C$26-1,0.3,0)+IF(0=Supuestos!$C$26,0.25,0)+IF(0=Supuestos!$C$26+2,0.25,0)+IF(0=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="C12" s="8">
-        <f>Supuestos!$C$30*(IF(1=Supuestos!$C$26-1,0.3,0)+IF(1=Supuestos!$C$26,0.25,0)+IF(1=Supuestos!$C$26+2,0.25,0)+IF(1=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="D12" s="8">
-        <f>Supuestos!$C$30*(IF(2=Supuestos!$C$26-1,0.3,0)+IF(2=Supuestos!$C$26,0.25,0)+IF(2=Supuestos!$C$26+2,0.25,0)+IF(2=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>Supuestos!$C$30*(IF(3=Supuestos!$C$26-1,0.3,0)+IF(3=Supuestos!$C$26,0.25,0)+IF(3=Supuestos!$C$26+2,0.25,0)+IF(3=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="F12" s="8">
-        <f>Supuestos!$C$30*(IF(4=Supuestos!$C$26-1,0.3,0)+IF(4=Supuestos!$C$26,0.25,0)+IF(4=Supuestos!$C$26+2,0.25,0)+IF(4=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>Supuestos!$C$30*(IF(5=Supuestos!$C$26-1,0.3,0)+IF(5=Supuestos!$C$26,0.25,0)+IF(5=Supuestos!$C$26+2,0.25,0)+IF(5=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>Supuestos!$C$30*(IF(6=Supuestos!$C$26-1,0.3,0)+IF(6=Supuestos!$C$26,0.25,0)+IF(6=Supuestos!$C$26+2,0.25,0)+IF(6=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="I12" s="8">
-        <f>Supuestos!$C$30*(IF(7=Supuestos!$C$26-1,0.3,0)+IF(7=Supuestos!$C$26,0.25,0)+IF(7=Supuestos!$C$26+2,0.25,0)+IF(7=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>Supuestos!$C$30*(IF(8=Supuestos!$C$26-1,0.3,0)+IF(8=Supuestos!$C$26,0.25,0)+IF(8=Supuestos!$C$26+2,0.25,0)+IF(8=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
-        <f>Supuestos!$C$30*(IF(9=Supuestos!$C$26-1,0.3,0)+IF(9=Supuestos!$C$26,0.25,0)+IF(9=Supuestos!$C$26+2,0.25,0)+IF(9=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="L12" s="8">
-        <f>Supuestos!$C$30*(IF(10=Supuestos!$C$26-1,0.3,0)+IF(10=Supuestos!$C$26,0.25,0)+IF(10=Supuestos!$C$26+2,0.25,0)+IF(10=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="M12" s="8">
-        <f>Supuestos!$C$30*(IF(11=Supuestos!$C$26-1,0.3,0)+IF(11=Supuestos!$C$26,0.25,0)+IF(11=Supuestos!$C$26+2,0.25,0)+IF(11=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="N12" s="8">
-        <f>Supuestos!$C$30*(IF(12=Supuestos!$C$26-1,0.3,0)+IF(12=Supuestos!$C$26,0.25,0)+IF(12=Supuestos!$C$26+2,0.25,0)+IF(12=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="O12" s="8">
-        <f>Supuestos!$C$30*(IF(13=Supuestos!$C$26-1,0.3,0)+IF(13=Supuestos!$C$26,0.25,0)+IF(13=Supuestos!$C$26+2,0.25,0)+IF(13=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="P12" s="8">
-        <f>Supuestos!$C$30*(IF(14=Supuestos!$C$26-1,0.3,0)+IF(14=Supuestos!$C$26,0.25,0)+IF(14=Supuestos!$C$26+2,0.25,0)+IF(14=Supuestos!$C$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8">
-        <f>Supuestos!$C$30*(IF(15=Supuestos!$C$26-1,0.3,0)+IF(15=Supuestos!$C$26,0.25,0)+IF(15=Supuestos!$C$26+2,0.25,0)+IF(15=Supuestos!$C$26+4,0.2,0))</f>
+          <t>Urbanización (3 macro-etapas)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Supuestos!$C$30*(IF(0=Supuestos!$C$26-1,0.45,0)+IF(0=Supuestos!$C$26+1,0.3,0)+IF(0=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>Supuestos!$C$30*(IF(1=Supuestos!$C$26-1,0.45,0)+IF(1=Supuestos!$C$26+1,0.3,0)+IF(1=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>Supuestos!$C$30*(IF(2=Supuestos!$C$26-1,0.45,0)+IF(2=Supuestos!$C$26+1,0.3,0)+IF(2=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>Supuestos!$C$30*(IF(3=Supuestos!$C$26-1,0.45,0)+IF(3=Supuestos!$C$26+1,0.3,0)+IF(3=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>Supuestos!$C$30*(IF(4=Supuestos!$C$26-1,0.45,0)+IF(4=Supuestos!$C$26+1,0.3,0)+IF(4=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>Supuestos!$C$30*(IF(5=Supuestos!$C$26-1,0.45,0)+IF(5=Supuestos!$C$26+1,0.3,0)+IF(5=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>Supuestos!$C$30*(IF(6=Supuestos!$C$26-1,0.45,0)+IF(6=Supuestos!$C$26+1,0.3,0)+IF(6=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>Supuestos!$C$30*(IF(7=Supuestos!$C$26-1,0.45,0)+IF(7=Supuestos!$C$26+1,0.3,0)+IF(7=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>Supuestos!$C$30*(IF(8=Supuestos!$C$26-1,0.45,0)+IF(8=Supuestos!$C$26+1,0.3,0)+IF(8=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>Supuestos!$C$30*(IF(9=Supuestos!$C$26-1,0.45,0)+IF(9=Supuestos!$C$26+1,0.3,0)+IF(9=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>Supuestos!$C$30*(IF(10=Supuestos!$C$26-1,0.45,0)+IF(10=Supuestos!$C$26+1,0.3,0)+IF(10=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="9">
+        <f>Supuestos!$C$30*(IF(11=Supuestos!$C$26-1,0.45,0)+IF(11=Supuestos!$C$26+1,0.3,0)+IF(11=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>Supuestos!$C$30*(IF(12=Supuestos!$C$26-1,0.45,0)+IF(12=Supuestos!$C$26+1,0.3,0)+IF(12=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="O12" s="9">
+        <f>Supuestos!$C$30*(IF(13=Supuestos!$C$26-1,0.45,0)+IF(13=Supuestos!$C$26+1,0.3,0)+IF(13=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="P12" s="9">
+        <f>Supuestos!$C$30*(IF(14=Supuestos!$C$26-1,0.45,0)+IF(14=Supuestos!$C$26+1,0.3,0)+IF(14=Supuestos!$C$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9">
+        <f>Supuestos!$C$30*(IF(15=Supuestos!$C$26-1,0.45,0)+IF(15=Supuestos!$C$26+1,0.3,0)+IF(15=Supuestos!$C$26+3,0.25,0))</f>
         <v/>
       </c>
     </row>
@@ -3186,54 +3199,54 @@
           <t>Proyectos, permisos y especialidades</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>Supuestos!$C$33</f>
         <v/>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <f>Supuestos!$C$34</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="P13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3243,67 +3256,67 @@
           <t>Gasto comercial</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <f>B9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>O9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="9">
         <f>P9*Supuestos!$C$31</f>
         <v/>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="9">
         <f>Q9*Supuestos!$C$31</f>
         <v/>
       </c>
@@ -3314,209 +3327,209 @@
           <t>Administración y contribuciones</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <f>IF(OR(B7&gt;0,0&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>IF(OR(C7&gt;0,1&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>IF(OR(D7&gt;0,2&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>IF(OR(E7&gt;0,3&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>IF(OR(F7&gt;0,4&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>IF(OR(G7&gt;0,5&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>IF(OR(H7&gt;0,6&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>IF(OR(I7&gt;0,7&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>IF(OR(J7&gt;0,8&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>IF(OR(K7&gt;0,9&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>IF(OR(L7&gt;0,10&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>IF(OR(M7&gt;0,11&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>IF(OR(N7&gt;0,12&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="9">
         <f>IF(OR(O7&gt;0,13&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="9">
         <f>IF(OR(P7&gt;0,14&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="9">
         <f>IF(OR(Q7&gt;0,15&lt;Supuestos!$C$26),Supuestos!$C$32+Supuestos!$C$35,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Total egresos operacionales</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B12+B13+B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>C12+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>D12+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>E12+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>F12+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>G12+G13+G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>H12+H13+H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>I12+I13+I14+I15</f>
         <v/>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>J12+J13+J14+J15</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f>K12+K13+K14+K15</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>L12+L13+L14+L15</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="20">
         <f>M12+M13+M14+M15</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="20">
         <f>N12+N13+N14+N15</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="20">
         <f>O12+O13+O14+O15</f>
         <v/>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="20">
         <f>P12+P13+P14+P15</f>
         <v/>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="20">
         <f>Q12+Q13+Q14+Q15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Pago del terreno</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <f>Supuestos!$B$18</f>
         <v/>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>IF(1&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:B18)),MIN(C10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:B18))))</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f>IF(2&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:C18)),MIN(D10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:C18))))</f>
         <v/>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <f>IF(3&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:D18)),MIN(E10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:D18))))</f>
         <v/>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <f>IF(4&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:E18)),MIN(F10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:E18))))</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <f>IF(5&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:F18)),MIN(G10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:F18))))</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <f>IF(6&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:G18)),MIN(H10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:G18))))</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <f>IF(7&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:H18)),MIN(I10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:H18))))</f>
         <v/>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="9">
         <f>IF(8&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:I18)),MIN(J10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:I18))))</f>
         <v/>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <f>IF(9&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:J18)),MIN(K10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:J18))))</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="9">
         <f>IF(10&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:K18)),MIN(L10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:K18))))</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <f>IF(11&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:L18)),MIN(M10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:L18))))</f>
         <v/>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="9">
         <f>IF(12&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:M18)),MIN(N10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:M18))))</f>
         <v/>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="9">
         <f>IF(13&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:N18)),MIN(O10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:N18))))</f>
         <v/>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="9">
         <f>IF(14&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:O18)),MIN(P10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:O18))))</f>
         <v/>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="9">
         <f>IF(15&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:P18)),MIN(Q10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:P18))))</f>
         <v/>
       </c>
@@ -3527,67 +3540,67 @@
           <t>Saldo del terreno pendiente</t>
         </is>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:B18))</f>
         <v/>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:C18))</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:D18))</f>
         <v/>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:E18))</f>
         <v/>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:F18))</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:G18))</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:H18))</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:I18))</f>
         <v/>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:J18))</f>
         <v/>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:K18))</f>
         <v/>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:L18))</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:M18))</f>
         <v/>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:N18))</f>
         <v/>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:O18))</f>
         <v/>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:P18))</f>
         <v/>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:Q18))</f>
         <v/>
       </c>
@@ -3598,347 +3611,347 @@
           <t>Impuesto a la renta (pagado al año siguiente)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="8">
-        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8">
-        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="J20" s="8">
-        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="K20" s="8">
-        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="L20" s="8">
-        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="M20" s="8">
-        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="N20" s="8">
-        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="O20" s="8">
-        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="P20" s="8">
-        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="8">
-        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$C$36)</f>
+      <c r="C20" s="9">
+        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="K20" s="9">
+        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="L20" s="9">
+        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="M20" s="9">
+        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="N20" s="9">
+        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="O20" s="9">
+        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="P20" s="9">
+        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9">
+        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>FLUJO DE CAJA DEL PERÍODO</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="22">
         <f>B10-B16-B18-B20</f>
         <v/>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>C10-C16-C18-C20</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>D10-D16-D18-D20</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="22">
         <f>E10-E16-E18-E20</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="22">
         <f>F10-F16-F18-F20</f>
         <v/>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="22">
         <f>G10-G16-G18-G20</f>
         <v/>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <f>H10-H16-H18-H20</f>
         <v/>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <f>I10-I16-I18-I20</f>
         <v/>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="22">
         <f>J10-J16-J18-J20</f>
         <v/>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="22">
         <f>K10-K16-K18-K20</f>
         <v/>
       </c>
-      <c r="L22" s="21">
+      <c r="L22" s="22">
         <f>L10-L16-L18-L20</f>
         <v/>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="22">
         <f>M10-M16-M18-M20</f>
         <v/>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="22">
         <f>N10-N16-N18-N20</f>
         <v/>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="22">
         <f>O10-O16-O18-O20</f>
         <v/>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="22">
         <f>P10-P16-P18-P20</f>
         <v/>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="22">
         <f>Q10-Q16-Q18-Q20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Flujo acumulado</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <f>B22</f>
         <v/>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <f>B23+C22</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <f>C23+D22</f>
         <v/>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <f>D23+E22</f>
         <v/>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <f>E23+F22</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <f>F23+G22</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="9">
         <f>G23+H22</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f>H23+I22</f>
         <v/>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="9">
         <f>I23+J22</f>
         <v/>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <f>J23+K22</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>K23+L22</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f>L23+M22</f>
         <v/>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="9">
         <f>M23+N22</f>
         <v/>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="9">
         <f>N23+O22</f>
         <v/>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="9">
         <f>O23+P22</f>
         <v/>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="9">
         <f>P23+Q22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>INDICADORES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Ingresos totales</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="22">
         <f>SUM(B9:Q9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Costos totales (con terreno)</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="22">
         <f>SUM(B16:Q16)+Supuestos!$B$17*0.881</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Utilidad antes de impuesto</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="22">
         <f>B26-B27</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Margen bruto</t>
         </is>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="23">
         <f>B28/B26</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Impuesto</t>
         </is>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="22">
         <f>B28*Supuestos!$C$36</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Utilidad neta</t>
         </is>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="22">
         <f>B28-B30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Margen neto</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>B31/B26</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Capital máximo expuesto</t>
         </is>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="22">
         <f>-MIN(B23:Q23,0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>TIR del proyecto</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <f>IRR(B22:Q22)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>VAN a la tasa de descuento</t>
         </is>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <f>NPV(Supuestos!$C$37,C22:Q22)+B22</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Precio promedio logrado (UF/m²)</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>B26/Supuestos!$B$6</f>
+      <c r="B36" s="24">
+        <f>B26/Supuestos!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Saldo impago al vencer el plazo</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <f>INDEX(B19:Q19,Supuestos!$B$20+1)</f>
         <v/>
       </c>
@@ -3991,144 +4004,144 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Año 11</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Año 12</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>Año 13</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Año 14</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>Año 15</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="16" t="n">
+      <c r="M5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4138,139 +4151,139 @@
           <t>Sitios vendidos acumulados (previo)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <f>0</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <f>F6+F7</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <f>G6+G7</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
         <f>H6+H7</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="9">
         <f>I6+I7</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="9">
         <f>J6+J7</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="9">
         <f>K6+K7</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="9">
         <f>L6+L7</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="9">
         <f>M6+M7</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>N6+N7</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="9">
         <f>O6+O7</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="9">
         <f>P6+P7</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Sitios vendidos en el año</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>IF(0&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-B6))</f>
-        <v/>
-      </c>
-      <c r="C7" s="8">
-        <f>IF(1&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-C6))</f>
-        <v/>
-      </c>
-      <c r="D7" s="8">
-        <f>IF(2&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-D6))</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>IF(3&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-E6))</f>
-        <v/>
-      </c>
-      <c r="F7" s="8">
-        <f>IF(4&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-F6))</f>
-        <v/>
-      </c>
-      <c r="G7" s="8">
-        <f>IF(5&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-G6))</f>
-        <v/>
-      </c>
-      <c r="H7" s="8">
-        <f>IF(6&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-H6))</f>
-        <v/>
-      </c>
-      <c r="I7" s="8">
-        <f>IF(7&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-I6))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8">
-        <f>IF(8&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-J6))</f>
-        <v/>
-      </c>
-      <c r="K7" s="8">
-        <f>IF(9&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-K6))</f>
-        <v/>
-      </c>
-      <c r="L7" s="8">
-        <f>IF(10&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-L6))</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
-        <f>IF(11&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-M6))</f>
-        <v/>
-      </c>
-      <c r="N7" s="8">
-        <f>IF(12&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-N6))</f>
-        <v/>
-      </c>
-      <c r="O7" s="8">
-        <f>IF(13&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-O6))</f>
-        <v/>
-      </c>
-      <c r="P7" s="8">
-        <f>IF(14&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-P6))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8">
-        <f>IF(15&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$7-Q6))</f>
+      <c r="B7" s="9">
+        <f>IF(0&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="9">
+        <f>IF(1&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>IF(2&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>IF(3&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-E6))</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>IF(4&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-F6))</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(5&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-G6))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(6&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-H6))</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>IF(7&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-I6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>IF(8&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-J6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>IF(9&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-K6))</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IF(10&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-L6))</f>
+        <v/>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(11&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-M6))</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(12&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-N6))</f>
+        <v/>
+      </c>
+      <c r="O7" s="9">
+        <f>IF(13&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-O6))</f>
+        <v/>
+      </c>
+      <c r="P7" s="9">
+        <f>IF(14&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-P6))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="9">
+        <f>IF(15&lt;Supuestos!$D$26,0,MIN(Supuestos!$D$25,Supuestos!$B$8-Q6))</f>
         <v/>
       </c>
     </row>
@@ -4280,138 +4293,138 @@
           <t>Precio del año (UF/m²)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <f>IF(0&lt;Supuestos!$D$26,0,IF(0-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>IF(1&lt;Supuestos!$D$26,0,IF(1-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF(2&lt;Supuestos!$D$26,0,IF(2-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>IF(3&lt;Supuestos!$D$26,0,IF(3-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF(4&lt;Supuestos!$D$26,0,IF(4-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>IF(5&lt;Supuestos!$D$26,0,IF(5-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="18">
         <f>IF(6&lt;Supuestos!$D$26,0,IF(6-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="18">
         <f>IF(7&lt;Supuestos!$D$26,0,IF(7-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="18">
         <f>IF(8&lt;Supuestos!$D$26,0,IF(8-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="18">
         <f>IF(9&lt;Supuestos!$D$26,0,IF(9-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="18">
         <f>IF(10&lt;Supuestos!$D$26,0,IF(10-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="18">
         <f>IF(11&lt;Supuestos!$D$26,0,IF(11-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <f>IF(12&lt;Supuestos!$D$26,0,IF(12-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="18">
         <f>IF(13&lt;Supuestos!$D$26,0,IF(13-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="18">
         <f>IF(14&lt;Supuestos!$D$26,0,IF(14-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="18">
         <f>IF(15&lt;Supuestos!$D$26,0,IF(15-Supuestos!$D$26+1&gt;=Supuestos!$D$29,Supuestos!$D$28,Supuestos!$D$27))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Ingresos por venta</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <f>B7*Supuestos!$B$13*B8</f>
         <v/>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <f>C7*Supuestos!$B$13*C8</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>D7*Supuestos!$B$13*D8</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <f>E7*Supuestos!$B$13*E8</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <f>F7*Supuestos!$B$13*F8</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <f>G7*Supuestos!$B$13*G8</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <f>H7*Supuestos!$B$13*H8</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="9">
         <f>I7*Supuestos!$B$13*I8</f>
         <v/>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9">
         <f>J7*Supuestos!$B$13*J8</f>
         <v/>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="9">
         <f>K7*Supuestos!$B$13*K8</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="9">
         <f>L7*Supuestos!$B$13*L8</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="9">
         <f>M7*Supuestos!$B$13*M8</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="9">
         <f>N7*Supuestos!$B$13*N8</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>O7*Supuestos!$B$13*O8</f>
         <v/>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="9">
         <f>P7*Supuestos!$B$13*P8</f>
         <v/>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="9">
         <f>Q7*Supuestos!$B$13*Q8</f>
         <v/>
       </c>
@@ -4422,67 +4435,67 @@
           <t>Caja por ventas (20% anticipado)</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <f>B9*(1-Supuestos!$D$38)+C9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <f>C9*(1-Supuestos!$D$38)+D9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>D9*(1-Supuestos!$D$38)+E9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <f>E9*(1-Supuestos!$D$38)+F9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <f>F9*(1-Supuestos!$D$38)+G9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <f>G9*(1-Supuestos!$D$38)+H9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>H9*(1-Supuestos!$D$38)+I9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <f>I9*(1-Supuestos!$D$38)+J9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <f>J9*(1-Supuestos!$D$38)+K9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="9">
         <f>K9*(1-Supuestos!$D$38)+L9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="9">
         <f>L9*(1-Supuestos!$D$38)+M9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="9">
         <f>M9*(1-Supuestos!$D$38)+N9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="9">
         <f>N9*(1-Supuestos!$D$38)+O9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>O9*(1-Supuestos!$D$38)+P9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="9">
         <f>P9*(1-Supuestos!$D$38)+Q9*Supuestos!$D$38</f>
         <v/>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="9">
         <f>Q9*(1-Supuestos!$D$38)</f>
         <v/>
       </c>
@@ -4490,71 +4503,71 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Urbanización (4 macro-etapas)</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Supuestos!$D$30*(IF(0=Supuestos!$D$26-1,0.3,0)+IF(0=Supuestos!$D$26,0.25,0)+IF(0=Supuestos!$D$26+2,0.25,0)+IF(0=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="C12" s="8">
-        <f>Supuestos!$D$30*(IF(1=Supuestos!$D$26-1,0.3,0)+IF(1=Supuestos!$D$26,0.25,0)+IF(1=Supuestos!$D$26+2,0.25,0)+IF(1=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="D12" s="8">
-        <f>Supuestos!$D$30*(IF(2=Supuestos!$D$26-1,0.3,0)+IF(2=Supuestos!$D$26,0.25,0)+IF(2=Supuestos!$D$26+2,0.25,0)+IF(2=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>Supuestos!$D$30*(IF(3=Supuestos!$D$26-1,0.3,0)+IF(3=Supuestos!$D$26,0.25,0)+IF(3=Supuestos!$D$26+2,0.25,0)+IF(3=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="F12" s="8">
-        <f>Supuestos!$D$30*(IF(4=Supuestos!$D$26-1,0.3,0)+IF(4=Supuestos!$D$26,0.25,0)+IF(4=Supuestos!$D$26+2,0.25,0)+IF(4=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>Supuestos!$D$30*(IF(5=Supuestos!$D$26-1,0.3,0)+IF(5=Supuestos!$D$26,0.25,0)+IF(5=Supuestos!$D$26+2,0.25,0)+IF(5=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>Supuestos!$D$30*(IF(6=Supuestos!$D$26-1,0.3,0)+IF(6=Supuestos!$D$26,0.25,0)+IF(6=Supuestos!$D$26+2,0.25,0)+IF(6=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="I12" s="8">
-        <f>Supuestos!$D$30*(IF(7=Supuestos!$D$26-1,0.3,0)+IF(7=Supuestos!$D$26,0.25,0)+IF(7=Supuestos!$D$26+2,0.25,0)+IF(7=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>Supuestos!$D$30*(IF(8=Supuestos!$D$26-1,0.3,0)+IF(8=Supuestos!$D$26,0.25,0)+IF(8=Supuestos!$D$26+2,0.25,0)+IF(8=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
-        <f>Supuestos!$D$30*(IF(9=Supuestos!$D$26-1,0.3,0)+IF(9=Supuestos!$D$26,0.25,0)+IF(9=Supuestos!$D$26+2,0.25,0)+IF(9=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="L12" s="8">
-        <f>Supuestos!$D$30*(IF(10=Supuestos!$D$26-1,0.3,0)+IF(10=Supuestos!$D$26,0.25,0)+IF(10=Supuestos!$D$26+2,0.25,0)+IF(10=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="M12" s="8">
-        <f>Supuestos!$D$30*(IF(11=Supuestos!$D$26-1,0.3,0)+IF(11=Supuestos!$D$26,0.25,0)+IF(11=Supuestos!$D$26+2,0.25,0)+IF(11=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="N12" s="8">
-        <f>Supuestos!$D$30*(IF(12=Supuestos!$D$26-1,0.3,0)+IF(12=Supuestos!$D$26,0.25,0)+IF(12=Supuestos!$D$26+2,0.25,0)+IF(12=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="O12" s="8">
-        <f>Supuestos!$D$30*(IF(13=Supuestos!$D$26-1,0.3,0)+IF(13=Supuestos!$D$26,0.25,0)+IF(13=Supuestos!$D$26+2,0.25,0)+IF(13=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="P12" s="8">
-        <f>Supuestos!$D$30*(IF(14=Supuestos!$D$26-1,0.3,0)+IF(14=Supuestos!$D$26,0.25,0)+IF(14=Supuestos!$D$26+2,0.25,0)+IF(14=Supuestos!$D$26+4,0.2,0))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8">
-        <f>Supuestos!$D$30*(IF(15=Supuestos!$D$26-1,0.3,0)+IF(15=Supuestos!$D$26,0.25,0)+IF(15=Supuestos!$D$26+2,0.25,0)+IF(15=Supuestos!$D$26+4,0.2,0))</f>
+          <t>Urbanización (3 macro-etapas)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Supuestos!$D$30*(IF(0=Supuestos!$D$26-1,0.45,0)+IF(0=Supuestos!$D$26+1,0.3,0)+IF(0=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>Supuestos!$D$30*(IF(1=Supuestos!$D$26-1,0.45,0)+IF(1=Supuestos!$D$26+1,0.3,0)+IF(1=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>Supuestos!$D$30*(IF(2=Supuestos!$D$26-1,0.45,0)+IF(2=Supuestos!$D$26+1,0.3,0)+IF(2=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>Supuestos!$D$30*(IF(3=Supuestos!$D$26-1,0.45,0)+IF(3=Supuestos!$D$26+1,0.3,0)+IF(3=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>Supuestos!$D$30*(IF(4=Supuestos!$D$26-1,0.45,0)+IF(4=Supuestos!$D$26+1,0.3,0)+IF(4=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>Supuestos!$D$30*(IF(5=Supuestos!$D$26-1,0.45,0)+IF(5=Supuestos!$D$26+1,0.3,0)+IF(5=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>Supuestos!$D$30*(IF(6=Supuestos!$D$26-1,0.45,0)+IF(6=Supuestos!$D$26+1,0.3,0)+IF(6=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>Supuestos!$D$30*(IF(7=Supuestos!$D$26-1,0.45,0)+IF(7=Supuestos!$D$26+1,0.3,0)+IF(7=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>Supuestos!$D$30*(IF(8=Supuestos!$D$26-1,0.45,0)+IF(8=Supuestos!$D$26+1,0.3,0)+IF(8=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="9">
+        <f>Supuestos!$D$30*(IF(9=Supuestos!$D$26-1,0.45,0)+IF(9=Supuestos!$D$26+1,0.3,0)+IF(9=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>Supuestos!$D$30*(IF(10=Supuestos!$D$26-1,0.45,0)+IF(10=Supuestos!$D$26+1,0.3,0)+IF(10=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="9">
+        <f>Supuestos!$D$30*(IF(11=Supuestos!$D$26-1,0.45,0)+IF(11=Supuestos!$D$26+1,0.3,0)+IF(11=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>Supuestos!$D$30*(IF(12=Supuestos!$D$26-1,0.45,0)+IF(12=Supuestos!$D$26+1,0.3,0)+IF(12=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="O12" s="9">
+        <f>Supuestos!$D$30*(IF(13=Supuestos!$D$26-1,0.45,0)+IF(13=Supuestos!$D$26+1,0.3,0)+IF(13=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="P12" s="9">
+        <f>Supuestos!$D$30*(IF(14=Supuestos!$D$26-1,0.45,0)+IF(14=Supuestos!$D$26+1,0.3,0)+IF(14=Supuestos!$D$26+3,0.25,0))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="9">
+        <f>Supuestos!$D$30*(IF(15=Supuestos!$D$26-1,0.45,0)+IF(15=Supuestos!$D$26+1,0.3,0)+IF(15=Supuestos!$D$26+3,0.25,0))</f>
         <v/>
       </c>
     </row>
@@ -4564,54 +4577,54 @@
           <t>Proyectos, permisos y especialidades</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>Supuestos!$D$33</f>
         <v/>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <f>Supuestos!$D$34</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="P13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4621,67 +4634,67 @@
           <t>Gasto comercial</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <f>B9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>O9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="9">
         <f>P9*Supuestos!$D$31</f>
         <v/>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="9">
         <f>Q9*Supuestos!$D$31</f>
         <v/>
       </c>
@@ -4692,209 +4705,209 @@
           <t>Administración y contribuciones</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <f>IF(OR(B7&gt;0,0&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>IF(OR(C7&gt;0,1&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>IF(OR(D7&gt;0,2&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>IF(OR(E7&gt;0,3&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>IF(OR(F7&gt;0,4&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>IF(OR(G7&gt;0,5&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>IF(OR(H7&gt;0,6&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>IF(OR(I7&gt;0,7&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>IF(OR(J7&gt;0,8&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>IF(OR(K7&gt;0,9&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>IF(OR(L7&gt;0,10&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>IF(OR(M7&gt;0,11&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>IF(OR(N7&gt;0,12&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="9">
         <f>IF(OR(O7&gt;0,13&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="9">
         <f>IF(OR(P7&gt;0,14&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="9">
         <f>IF(OR(Q7&gt;0,15&lt;Supuestos!$D$26),Supuestos!$D$32+Supuestos!$D$35,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Total egresos operacionales</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B12+B13+B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>C12+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>D12+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>E12+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>F12+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>G12+G13+G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>H12+H13+H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>I12+I13+I14+I15</f>
         <v/>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>J12+J13+J14+J15</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f>K12+K13+K14+K15</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>L12+L13+L14+L15</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="20">
         <f>M12+M13+M14+M15</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="20">
         <f>N12+N13+N14+N15</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="20">
         <f>O12+O13+O14+O15</f>
         <v/>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="20">
         <f>P12+P13+P14+P15</f>
         <v/>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="20">
         <f>Q12+Q13+Q14+Q15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Pago del terreno</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <f>Supuestos!$B$18</f>
         <v/>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>IF(1&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:B18)),MIN(C10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:B18))))</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f>IF(2&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:C18)),MIN(D10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:C18))))</f>
         <v/>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <f>IF(3&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:D18)),MIN(E10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:D18))))</f>
         <v/>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <f>IF(4&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:E18)),MIN(F10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:E18))))</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <f>IF(5&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:F18)),MIN(G10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:F18))))</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <f>IF(6&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:G18)),MIN(H10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:G18))))</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <f>IF(7&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:H18)),MIN(I10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:H18))))</f>
         <v/>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="9">
         <f>IF(8&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:I18)),MIN(J10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:I18))))</f>
         <v/>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <f>IF(9&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:J18)),MIN(K10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:J18))))</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="9">
         <f>IF(10&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:K18)),MIN(L10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:K18))))</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <f>IF(11&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:L18)),MIN(M10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:L18))))</f>
         <v/>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="9">
         <f>IF(12&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:M18)),MIN(N10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:M18))))</f>
         <v/>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="9">
         <f>IF(13&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:N18)),MIN(O10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:N18))))</f>
         <v/>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="9">
         <f>IF(14&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:O18)),MIN(P10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:O18))))</f>
         <v/>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="9">
         <f>IF(15&gt;=Supuestos!$B$20,MAX(0,Supuestos!$B$17-SUM($B18:P18)),MIN(Q10*Supuestos!$B$19,MAX(0,Supuestos!$B$17-SUM($B18:P18))))</f>
         <v/>
       </c>
@@ -4905,67 +4918,67 @@
           <t>Saldo del terreno pendiente</t>
         </is>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:B18))</f>
         <v/>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:C18))</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:D18))</f>
         <v/>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:E18))</f>
         <v/>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:F18))</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:G18))</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:H18))</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:I18))</f>
         <v/>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:J18))</f>
         <v/>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:K18))</f>
         <v/>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:L18))</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:M18))</f>
         <v/>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:N18))</f>
         <v/>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:O18))</f>
         <v/>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:P18))</f>
         <v/>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="9">
         <f>MAX(0,Supuestos!$B$17-SUM($B18:Q18))</f>
         <v/>
       </c>
@@ -4976,347 +4989,347 @@
           <t>Impuesto a la renta (pagado al año siguiente)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="8">
-        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8">
-        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="J20" s="8">
-        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="K20" s="8">
-        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="L20" s="8">
-        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="M20" s="8">
-        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="N20" s="8">
-        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="O20" s="8">
-        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="P20" s="8">
-        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="8">
-        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$7)*Supuestos!$D$36)</f>
+      <c r="C20" s="9">
+        <f>MAX(0,(B9-B16-B7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>MAX(0,(C9-C16-C7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>MAX(0,(D9-D16-D7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>MAX(0,(E9-E16-E7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>MAX(0,(F9-F16-F7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>MAX(0,(G9-G16-G7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>MAX(0,(H9-H16-H7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>MAX(0,(I9-I16-I7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="K20" s="9">
+        <f>MAX(0,(J9-J16-J7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="L20" s="9">
+        <f>MAX(0,(K9-K16-K7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="M20" s="9">
+        <f>MAX(0,(L9-L16-L7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="N20" s="9">
+        <f>MAX(0,(M9-M16-M7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="O20" s="9">
+        <f>MAX(0,(N9-N16-N7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="P20" s="9">
+        <f>MAX(0,(O9-O16-O7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="9">
+        <f>MAX(0,(P9-P16-P7*Supuestos!$B$17*0.881/Supuestos!$B$8)*Supuestos!$D$36)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>FLUJO DE CAJA DEL PERÍODO</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="22">
         <f>B10-B16-B18-B20</f>
         <v/>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>C10-C16-C18-C20</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>D10-D16-D18-D20</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="22">
         <f>E10-E16-E18-E20</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="22">
         <f>F10-F16-F18-F20</f>
         <v/>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="22">
         <f>G10-G16-G18-G20</f>
         <v/>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <f>H10-H16-H18-H20</f>
         <v/>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <f>I10-I16-I18-I20</f>
         <v/>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="22">
         <f>J10-J16-J18-J20</f>
         <v/>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="22">
         <f>K10-K16-K18-K20</f>
         <v/>
       </c>
-      <c r="L22" s="21">
+      <c r="L22" s="22">
         <f>L10-L16-L18-L20</f>
         <v/>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="22">
         <f>M10-M16-M18-M20</f>
         <v/>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="22">
         <f>N10-N16-N18-N20</f>
         <v/>
       </c>
-      <c r="O22" s="21">
+      <c r="O22" s="22">
         <f>O10-O16-O18-O20</f>
         <v/>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="22">
         <f>P10-P16-P18-P20</f>
         <v/>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="22">
         <f>Q10-Q16-Q18-Q20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Flujo acumulado</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <f>B22</f>
         <v/>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <f>B23+C22</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <f>C23+D22</f>
         <v/>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <f>D23+E22</f>
         <v/>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <f>E23+F22</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <f>F23+G22</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="9">
         <f>G23+H22</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f>H23+I22</f>
         <v/>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="9">
         <f>I23+J22</f>
         <v/>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <f>J23+K22</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>K23+L22</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f>L23+M22</f>
         <v/>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="9">
         <f>M23+N22</f>
         <v/>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="9">
         <f>N23+O22</f>
         <v/>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="9">
         <f>O23+P22</f>
         <v/>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="9">
         <f>P23+Q22</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>INDICADORES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Ingresos totales</t>
         </is>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="22">
         <f>SUM(B9:Q9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Costos totales (con terreno)</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="22">
         <f>SUM(B16:Q16)+Supuestos!$B$17*0.881</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Utilidad antes de impuesto</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="22">
         <f>B26-B27</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Margen bruto</t>
         </is>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="23">
         <f>B28/B26</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Impuesto</t>
         </is>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="22">
         <f>B28*Supuestos!$D$36</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Utilidad neta</t>
         </is>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="22">
         <f>B28-B30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Margen neto</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>B31/B26</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Capital máximo expuesto</t>
         </is>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="22">
         <f>-MIN(B23:Q23,0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>TIR del proyecto</t>
         </is>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="23">
         <f>IRR(B22:Q22)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>VAN a la tasa de descuento</t>
         </is>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <f>NPV(Supuestos!$D$37,C22:Q22)+B22</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Precio promedio logrado (UF/m²)</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>B26/Supuestos!$B$6</f>
+      <c r="B36" s="24">
+        <f>B26/Supuestos!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Saldo impago al vencer el plazo</t>
         </is>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <f>INDEX(B19:Q19,Supuestos!$B$20+1)</f>
         <v/>
       </c>
@@ -5350,52 +5363,52 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ETAPA 2 — STRIP CENTER (terreno 4.386 m²)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Superficie arrendable (m²)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>619.2</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>619.2</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>619.2</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5405,18 +5418,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Superficie construida total (m²)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>729.7</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>729.7</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>729.7</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5426,18 +5439,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Renta (UF/m²/mes)</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>0.28</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.35</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>0.42</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5447,18 +5460,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>NOI de 4 canchas de pádel (UF/año)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>1350</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5468,18 +5481,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Inversión en canchas de pádel (UF)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>4200</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>3200</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5489,35 +5502,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Vacancia</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Costo de construcción (UF/m²)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>22</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5527,18 +5540,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Obras exteriores y empalmes (UF)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>4500</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>4500</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>4500</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -5548,18 +5561,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Costos blandos</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5569,18 +5582,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Terreno asignado (UF)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>2710</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>2710</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>2710</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5590,18 +5603,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Gastos no recuperables</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5611,18 +5624,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Cap rate de salida</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="15" t="n">
         <v>0.095</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>0.075</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5632,181 +5645,181 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Inversión total (UF)</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <f>B6*B11*(1+B13)+B9+B12+B14</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <f>C6*C11*(1+C13)+C9+C12+C14</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <f>D6*D11*(1+D13)+D9+D12+D14</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Renta bruta anual (UF)</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="22">
         <f>B5*B7*12</f>
         <v/>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <f>C5*C7*12</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="22">
         <f>D5*D7*12</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>NOI anual (UF)</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="22">
         <f>B18*(1-B10)*(1-B15)+B8</f>
         <v/>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="22">
         <f>C18*(1-C10)*(1-C15)+C8</f>
         <v/>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="22">
         <f>D18*(1-D10)*(1-D15)+D8</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Yield on cost</t>
         </is>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="23">
         <f>B19/B17</f>
         <v/>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>C19/C17</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>D19/D17</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Valor estabilizado (UF)</t>
         </is>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="22">
         <f>B19/B16</f>
         <v/>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <f>C19/C16</f>
         <v/>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <f>D19/D16</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Creación de valor (UF)</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="22">
         <f>B21-B17</f>
         <v/>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>C21-C17</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>D21-D17</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Payback (años)</t>
         </is>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="25">
         <f>B17/B19</f>
         <v/>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <f>C17/C19</f>
         <v/>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="25">
         <f>D17/D19</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>ETAPA 3 — COMPARACIÓN DE ALTERNATIVAS PARA EL PAÑO NORTE (18.619 m²)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Colegio build-to-suit</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Venta del paño</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>EDS arrendada</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Inversión propia (UF)</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <v>177894</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="26" t="n">
         <v>4879</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5816,18 +5829,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Flujo anual (UF)</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <v>12286</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="26" t="n">
         <v>4200</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5837,35 +5850,35 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Rentabilidad sobre costo</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>0.861</v>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Valor del activo (UF)</t>
         </is>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <v>144541</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>45885</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="26" t="n">
         <v>56000</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -5875,18 +5888,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Creación de valor (UF)</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="26" t="n">
         <v>-33352</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="26" t="n">
         <v>34383</v>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="26" t="n">
         <v>51121</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5896,35 +5909,35 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Payback (años)</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="28" t="n">
         <v>14.5</v>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="27" t="n">
+      <c r="D33" s="28" t="n">
         <v>1.2</v>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Superficie que ocupa (m²)</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="26" t="n">
         <v>18354</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="26" t="n">
         <v>18354</v>
       </c>
-      <c r="D34" s="25" t="n">
+      <c r="D34" s="26" t="n">
         <v>2200</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5934,7 +5947,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Requisito duro para la EDS: TMDA de Av. San Miguel sobre 8.000–12.000 veh/día para atraer a un operador de marca. Verificar en Dirección de Vialidad del Maule.</t>
         </is>
